--- a/raw/Timetable_2026Autumn_2026LE.xlsx
+++ b/raw/Timetable_2026Autumn_2026LE.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30606"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="122" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8595E935-3E0A-40B2-A3F8-EDBF2874122D}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{641C103D-4D6C-4DE5-BE4F-F4A2981D6A8C}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1088,6 +1088,78 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1115,81 +1187,9 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1535,81 +1535,81 @@
   <sheetData>
     <row r="1" spans="1:27"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="64" t="s">
+      <c r="C2" s="70"/>
+      <c r="D2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="64" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="65"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="64" t="s">
+      <c r="H2" s="50"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="65"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="64" t="s">
+      <c r="K2" s="50"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="65"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="64" t="s">
+      <c r="N2" s="50"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="64" t="s">
+      <c r="Q2" s="50"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="65"/>
-      <c r="U2" s="66"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="51"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="77"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="64" t="s">
+      <c r="A3" s="68"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="65"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="64" t="s">
+      <c r="E3" s="50"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="65"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="64" t="s">
+      <c r="H3" s="50"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="65"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="64" t="s">
+      <c r="K3" s="50"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="65"/>
-      <c r="O3" s="66"/>
-      <c r="P3" s="64" t="s">
+      <c r="N3" s="50"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="66"/>
-      <c r="S3" s="64" t="s">
+      <c r="Q3" s="50"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="58">
+      <c r="A4" s="61">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1663,7 +1663,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="59"/>
+      <c r="A5" s="62"/>
       <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
@@ -1711,7 +1711,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="59"/>
+      <c r="A6" s="62"/>
       <c r="B6" s="6" t="s">
         <v>26</v>
       </c>
@@ -1771,7 +1771,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="59"/>
+      <c r="A7" s="62"/>
       <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
@@ -1817,7 +1817,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="59"/>
+      <c r="A8" s="62"/>
       <c r="B8" s="6" t="s">
         <v>36</v>
       </c>
@@ -1875,7 +1875,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="59"/>
+      <c r="A9" s="62"/>
       <c r="B9" s="6" t="s">
         <v>38</v>
       </c>
@@ -1925,7 +1925,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="60"/>
+      <c r="A10" s="63"/>
       <c r="B10" s="6" t="s">
         <v>42</v>
       </c>
@@ -1969,7 +1969,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="61">
+      <c r="A11" s="64">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -2031,7 +2031,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="62"/>
+      <c r="A12" s="65"/>
       <c r="B12" s="11" t="s">
         <v>49</v>
       </c>
@@ -2077,7 +2077,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="62"/>
+      <c r="A13" s="65"/>
       <c r="B13" s="11" t="s">
         <v>50</v>
       </c>
@@ -2147,7 +2147,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="62"/>
+      <c r="A14" s="65"/>
       <c r="B14" s="11" t="s">
         <v>54</v>
       </c>
@@ -2183,7 +2183,7 @@
       <c r="AA14" s="7"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="62"/>
+      <c r="A15" s="65"/>
       <c r="B15" s="11" t="s">
         <v>55</v>
       </c>
@@ -2224,7 +2224,7 @@
       <c r="U15" s="14"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="62"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="11" t="s">
         <v>56</v>
       </c>
@@ -2259,7 +2259,7 @@
       <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="63"/>
+      <c r="A17" s="66"/>
       <c r="B17" s="11" t="s">
         <v>57</v>
       </c>
@@ -2286,7 +2286,7 @@
       <c r="U17" s="14"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="58">
+      <c r="A18" s="61">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -2331,7 +2331,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="59"/>
+      <c r="A19" s="62"/>
       <c r="B19" s="6" t="s">
         <v>59</v>
       </c>
@@ -2362,7 +2362,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="59"/>
+      <c r="A20" s="62"/>
       <c r="B20" s="6" t="s">
         <v>60</v>
       </c>
@@ -2417,7 +2417,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="59"/>
+      <c r="A21" s="62"/>
       <c r="B21" s="6" t="s">
         <v>61</v>
       </c>
@@ -2448,7 +2448,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="59"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="6" t="s">
         <v>62</v>
       </c>
@@ -2489,7 +2489,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="59"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="6" t="s">
         <v>63</v>
       </c>
@@ -2516,7 +2516,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="60"/>
+      <c r="A24" s="63"/>
       <c r="B24" s="18" t="s">
         <v>64</v>
       </c>
@@ -2543,7 +2543,7 @@
       <c r="U24" s="24"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="61">
+      <c r="A25" s="64">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -2588,7 +2588,7 @@
       <c r="U25" s="14"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="62"/>
+      <c r="A26" s="65"/>
       <c r="B26" s="11" t="s">
         <v>66</v>
       </c>
@@ -2619,7 +2619,7 @@
       <c r="U26" s="14"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="62"/>
+      <c r="A27" s="65"/>
       <c r="B27" s="11" t="s">
         <v>67</v>
       </c>
@@ -2674,7 +2674,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="62"/>
+      <c r="A28" s="65"/>
       <c r="B28" s="11" t="s">
         <v>68</v>
       </c>
@@ -2705,90 +2705,90 @@
       <c r="U28" s="14"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="62"/>
+      <c r="A29" s="65"/>
       <c r="B29" s="28" t="s">
         <v>69</v>
       </c>
       <c r="C29" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="67" t="s">
+      <c r="D29" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="68"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="68"/>
-      <c r="M29" s="68"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="68"/>
-      <c r="P29" s="68"/>
-      <c r="Q29" s="68"/>
-      <c r="R29" s="68"/>
-      <c r="S29" s="68"/>
-      <c r="T29" s="68"/>
-      <c r="U29" s="69"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="53"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="53"/>
+      <c r="S29" s="53"/>
+      <c r="T29" s="53"/>
+      <c r="U29" s="54"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="62"/>
+      <c r="A30" s="65"/>
       <c r="B30" s="28" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="70"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="71"/>
-      <c r="O30" s="71"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
-      <c r="R30" s="71"/>
-      <c r="S30" s="71"/>
-      <c r="T30" s="71"/>
-      <c r="U30" s="72"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="56"/>
+      <c r="R30" s="56"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="56"/>
+      <c r="U30" s="57"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="63"/>
+      <c r="A31" s="66"/>
       <c r="B31" s="28" t="s">
         <v>72</v>
       </c>
       <c r="C31" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="73"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="74"/>
-      <c r="R31" s="74"/>
-      <c r="S31" s="74"/>
-      <c r="T31" s="74"/>
-      <c r="U31" s="75"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="59"/>
+      <c r="M31" s="59"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="59"/>
+      <c r="P31" s="59"/>
+      <c r="Q31" s="59"/>
+      <c r="R31" s="59"/>
+      <c r="S31" s="59"/>
+      <c r="T31" s="59"/>
+      <c r="U31" s="60"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="58">
+      <c r="A32" s="61">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -2833,7 +2833,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="59"/>
+      <c r="A33" s="62"/>
       <c r="B33" s="6" t="s">
         <v>74</v>
       </c>
@@ -2864,7 +2864,7 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="59"/>
+      <c r="A34" s="62"/>
       <c r="B34" s="6" t="s">
         <v>75</v>
       </c>
@@ -2907,117 +2907,117 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="59"/>
+      <c r="A35" s="62"/>
       <c r="B35" s="30" t="s">
         <v>76</v>
       </c>
       <c r="C35" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="67" t="s">
+      <c r="D35" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
-      <c r="H35" s="68"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
-      <c r="L35" s="68"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="68"/>
-      <c r="O35" s="68"/>
-      <c r="P35" s="68"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="68"/>
-      <c r="S35" s="68"/>
-      <c r="T35" s="68"/>
-      <c r="U35" s="69"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="53"/>
+      <c r="P35" s="53"/>
+      <c r="Q35" s="53"/>
+      <c r="R35" s="53"/>
+      <c r="S35" s="53"/>
+      <c r="T35" s="53"/>
+      <c r="U35" s="54"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="59"/>
+      <c r="A36" s="62"/>
       <c r="B36" s="30" t="s">
         <v>77</v>
       </c>
       <c r="C36" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="70"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="71"/>
-      <c r="M36" s="71"/>
-      <c r="N36" s="71"/>
-      <c r="O36" s="71"/>
-      <c r="P36" s="71"/>
-      <c r="Q36" s="71"/>
-      <c r="R36" s="71"/>
-      <c r="S36" s="71"/>
-      <c r="T36" s="71"/>
-      <c r="U36" s="72"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="56"/>
+      <c r="O36" s="56"/>
+      <c r="P36" s="56"/>
+      <c r="Q36" s="56"/>
+      <c r="R36" s="56"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="56"/>
+      <c r="U36" s="57"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="59"/>
+      <c r="A37" s="62"/>
       <c r="B37" s="30" t="s">
         <v>78</v>
       </c>
       <c r="C37" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="70"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="71"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="71"/>
-      <c r="K37" s="71"/>
-      <c r="L37" s="71"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="71"/>
-      <c r="O37" s="71"/>
-      <c r="P37" s="71"/>
-      <c r="Q37" s="71"/>
-      <c r="R37" s="71"/>
-      <c r="S37" s="71"/>
-      <c r="T37" s="71"/>
-      <c r="U37" s="72"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="56"/>
+      <c r="O37" s="56"/>
+      <c r="P37" s="56"/>
+      <c r="Q37" s="56"/>
+      <c r="R37" s="56"/>
+      <c r="S37" s="56"/>
+      <c r="T37" s="56"/>
+      <c r="U37" s="57"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="60"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="30" t="s">
         <v>79</v>
       </c>
       <c r="C38" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="70"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="71"/>
-      <c r="L38" s="71"/>
-      <c r="M38" s="71"/>
-      <c r="N38" s="71"/>
-      <c r="O38" s="71"/>
-      <c r="P38" s="71"/>
-      <c r="Q38" s="71"/>
-      <c r="R38" s="71"/>
-      <c r="S38" s="71"/>
-      <c r="T38" s="71"/>
-      <c r="U38" s="72"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="56"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="56"/>
+      <c r="R38" s="56"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="56"/>
+      <c r="U38" s="57"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="61">
+      <c r="A39" s="64">
         <v>6</v>
       </c>
       <c r="B39" s="30" t="s">
@@ -3026,81 +3026,81 @@
       <c r="C39" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="70"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
-      <c r="L39" s="71"/>
-      <c r="M39" s="71"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="71"/>
-      <c r="P39" s="71"/>
-      <c r="Q39" s="71"/>
-      <c r="R39" s="71"/>
-      <c r="S39" s="71"/>
-      <c r="T39" s="71"/>
-      <c r="U39" s="72"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="56"/>
+      <c r="N39" s="56"/>
+      <c r="O39" s="56"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="56"/>
+      <c r="R39" s="56"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="56"/>
+      <c r="U39" s="57"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="62"/>
+      <c r="A40" s="65"/>
       <c r="B40" s="30" t="s">
         <v>81</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="70"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="71"/>
-      <c r="K40" s="71"/>
-      <c r="L40" s="71"/>
-      <c r="M40" s="71"/>
-      <c r="N40" s="71"/>
-      <c r="O40" s="71"/>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="71"/>
-      <c r="R40" s="71"/>
-      <c r="S40" s="71"/>
-      <c r="T40" s="71"/>
-      <c r="U40" s="72"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="56"/>
+      <c r="O40" s="56"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="56"/>
+      <c r="S40" s="56"/>
+      <c r="T40" s="56"/>
+      <c r="U40" s="57"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="62"/>
+      <c r="A41" s="65"/>
       <c r="B41" s="30" t="s">
         <v>82</v>
       </c>
       <c r="C41" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="73"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="74"/>
-      <c r="I41" s="74"/>
-      <c r="J41" s="74"/>
-      <c r="K41" s="74"/>
-      <c r="L41" s="74"/>
-      <c r="M41" s="74"/>
-      <c r="N41" s="74"/>
-      <c r="O41" s="74"/>
-      <c r="P41" s="74"/>
-      <c r="Q41" s="74"/>
-      <c r="R41" s="74"/>
-      <c r="S41" s="74"/>
-      <c r="T41" s="74"/>
-      <c r="U41" s="75"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="59"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="59"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="59"/>
+      <c r="O41" s="59"/>
+      <c r="P41" s="59"/>
+      <c r="Q41" s="59"/>
+      <c r="R41" s="59"/>
+      <c r="S41" s="59"/>
+      <c r="T41" s="59"/>
+      <c r="U41" s="60"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="62"/>
+      <c r="A42" s="65"/>
       <c r="B42" s="31" t="s">
         <v>83</v>
       </c>
@@ -3131,7 +3131,7 @@
       <c r="U42" s="14"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="62"/>
+      <c r="A43" s="65"/>
       <c r="B43" s="31" t="s">
         <v>84</v>
       </c>
@@ -3160,7 +3160,7 @@
       <c r="U43" s="14"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="62"/>
+      <c r="A44" s="65"/>
       <c r="B44" s="32" t="s">
         <v>85</v>
       </c>
@@ -3187,7 +3187,7 @@
       <c r="U44" s="24"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="63"/>
+      <c r="A45" s="66"/>
       <c r="B45" s="31" t="s">
         <v>86</v>
       </c>
@@ -3214,7 +3214,7 @@
       <c r="U45" s="14"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="58">
+      <c r="A46" s="61">
         <v>7</v>
       </c>
       <c r="B46" s="33" t="s">
@@ -3259,7 +3259,7 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="59"/>
+      <c r="A47" s="62"/>
       <c r="B47" s="33" t="s">
         <v>88</v>
       </c>
@@ -3302,7 +3302,7 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="59"/>
+      <c r="A48" s="62"/>
       <c r="B48" s="33" t="s">
         <v>91</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="59"/>
+      <c r="A49" s="62"/>
       <c r="B49" s="33" t="s">
         <v>92</v>
       </c>
@@ -3388,7 +3388,7 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="59"/>
+      <c r="A50" s="62"/>
       <c r="B50" s="33" t="s">
         <v>93</v>
       </c>
@@ -3429,7 +3429,7 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="59"/>
+      <c r="A51" s="62"/>
       <c r="B51" s="33" t="s">
         <v>94</v>
       </c>
@@ -3464,7 +3464,7 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="60"/>
+      <c r="A52" s="63"/>
       <c r="B52" s="33" t="s">
         <v>95</v>
       </c>
@@ -3491,7 +3491,7 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="61">
+      <c r="A53" s="64">
         <v>8</v>
       </c>
       <c r="B53" s="31" t="s">
@@ -3536,7 +3536,7 @@
       <c r="U53" s="14"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="62"/>
+      <c r="A54" s="65"/>
       <c r="B54" s="31" t="s">
         <v>97</v>
       </c>
@@ -3579,7 +3579,7 @@
       <c r="U54" s="14"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="62"/>
+      <c r="A55" s="65"/>
       <c r="B55" s="31" t="s">
         <v>99</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>29</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>28</v>
@@ -3634,7 +3634,7 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="62"/>
+      <c r="A56" s="65"/>
       <c r="B56" s="31" t="s">
         <v>101</v>
       </c>
@@ -3677,7 +3677,7 @@
       <c r="U56" s="14"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="62"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="31" t="s">
         <v>102</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>29</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G57" s="11" t="s">
         <v>41</v>
@@ -3720,7 +3720,7 @@
       <c r="U57" s="14"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="62"/>
+      <c r="A58" s="65"/>
       <c r="B58" s="31" t="s">
         <v>103</v>
       </c>
@@ -3755,7 +3755,7 @@
       <c r="U58" s="14"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="63"/>
+      <c r="A59" s="66"/>
       <c r="B59" s="31" t="s">
         <v>104</v>
       </c>
@@ -3782,7 +3782,7 @@
       <c r="U59" s="14"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="58">
+      <c r="A60" s="61">
         <v>9</v>
       </c>
       <c r="B60" s="33" t="s">
@@ -3827,7 +3827,7 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="59"/>
+      <c r="A61" s="62"/>
       <c r="B61" s="33" t="s">
         <v>106</v>
       </c>
@@ -3870,7 +3870,7 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="59"/>
+      <c r="A62" s="62"/>
       <c r="B62" s="33" t="s">
         <v>107</v>
       </c>
@@ -3925,7 +3925,7 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="59"/>
+      <c r="A63" s="62"/>
       <c r="B63" s="33" t="s">
         <v>108</v>
       </c>
@@ -3968,7 +3968,7 @@
       <c r="U63" s="34"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="59"/>
+      <c r="A64" s="62"/>
       <c r="B64" s="33" t="s">
         <v>109</v>
       </c>
@@ -4011,7 +4011,7 @@
       <c r="U64" s="34"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="59"/>
+      <c r="A65" s="62"/>
       <c r="B65" s="33" t="s">
         <v>110</v>
       </c>
@@ -4046,7 +4046,7 @@
       <c r="U65" s="34"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="60"/>
+      <c r="A66" s="63"/>
       <c r="B66" s="33" t="s">
         <v>111</v>
       </c>
@@ -4073,7 +4073,7 @@
       <c r="U66" s="34"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="61">
+      <c r="A67" s="64">
         <v>10</v>
       </c>
       <c r="B67" s="31" t="s">
@@ -4118,7 +4118,7 @@
       <c r="U67" s="35"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="62"/>
+      <c r="A68" s="65"/>
       <c r="B68" s="31" t="s">
         <v>113</v>
       </c>
@@ -4161,7 +4161,7 @@
       <c r="U68" s="35"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="62"/>
+      <c r="A69" s="65"/>
       <c r="B69" s="31" t="s">
         <v>115</v>
       </c>
@@ -4204,7 +4204,7 @@
       <c r="U69" s="35"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="62"/>
+      <c r="A70" s="65"/>
       <c r="B70" s="31" t="s">
         <v>117</v>
       </c>
@@ -4247,7 +4247,7 @@
       <c r="U70" s="35"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="62"/>
+      <c r="A71" s="65"/>
       <c r="B71" s="31" t="s">
         <v>118</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="U71" s="35"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="62"/>
+      <c r="A72" s="65"/>
       <c r="B72" s="31" t="s">
         <v>119</v>
       </c>
@@ -4317,7 +4317,7 @@
       <c r="U72" s="35"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="63"/>
+      <c r="A73" s="66"/>
       <c r="B73" s="31" t="s">
         <v>120</v>
       </c>
@@ -4344,7 +4344,7 @@
       <c r="U73" s="35"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="58">
+      <c r="A74" s="61">
         <v>11</v>
       </c>
       <c r="B74" s="33" t="s">
@@ -4389,7 +4389,7 @@
       <c r="U74" s="34"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="59"/>
+      <c r="A75" s="62"/>
       <c r="B75" s="33" t="s">
         <v>122</v>
       </c>
@@ -4432,7 +4432,7 @@
       <c r="U75" s="34"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="59"/>
+      <c r="A76" s="62"/>
       <c r="B76" s="33" t="s">
         <v>123</v>
       </c>
@@ -4487,7 +4487,7 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="59"/>
+      <c r="A77" s="62"/>
       <c r="B77" s="33" t="s">
         <v>124</v>
       </c>
@@ -4530,7 +4530,7 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="59"/>
+      <c r="A78" s="62"/>
       <c r="B78" s="33" t="s">
         <v>125</v>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="59"/>
+      <c r="A79" s="62"/>
       <c r="B79" s="33" t="s">
         <v>126</v>
       </c>
@@ -4612,7 +4612,7 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="60"/>
+      <c r="A80" s="63"/>
       <c r="B80" s="33" t="s">
         <v>128</v>
       </c>
@@ -4639,7 +4639,7 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="61">
+      <c r="A81" s="64">
         <v>12</v>
       </c>
       <c r="B81" s="31" t="s">
@@ -4684,7 +4684,7 @@
       <c r="U81" s="14"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="62"/>
+      <c r="A82" s="65"/>
       <c r="B82" s="31" t="s">
         <v>130</v>
       </c>
@@ -4727,7 +4727,7 @@
       <c r="U82" s="14"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="62"/>
+      <c r="A83" s="65"/>
       <c r="B83" s="31" t="s">
         <v>131</v>
       </c>
@@ -4782,7 +4782,7 @@
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="62"/>
+      <c r="A84" s="65"/>
       <c r="B84" s="31" t="s">
         <v>134</v>
       </c>
@@ -4825,7 +4825,7 @@
       <c r="U84" s="14"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="62"/>
+      <c r="A85" s="65"/>
       <c r="B85" s="31" t="s">
         <v>135</v>
       </c>
@@ -4868,7 +4868,7 @@
       <c r="U85" s="14"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="62"/>
+      <c r="A86" s="65"/>
       <c r="B86" s="31" t="s">
         <v>136</v>
       </c>
@@ -4903,7 +4903,7 @@
       <c r="U86" s="14"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="63"/>
+      <c r="A87" s="66"/>
       <c r="B87" s="31" t="s">
         <v>137</v>
       </c>
@@ -4930,7 +4930,7 @@
       <c r="U87" s="14"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="58">
+      <c r="A88" s="61">
         <v>13</v>
       </c>
       <c r="B88" s="33" t="s">
@@ -4975,7 +4975,7 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="59"/>
+      <c r="A89" s="62"/>
       <c r="B89" s="33" t="s">
         <v>139</v>
       </c>
@@ -5018,7 +5018,7 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="59"/>
+      <c r="A90" s="62"/>
       <c r="B90" s="33" t="s">
         <v>140</v>
       </c>
@@ -5073,7 +5073,7 @@
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="59"/>
+      <c r="A91" s="62"/>
       <c r="B91" s="33" t="s">
         <v>141</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="59"/>
+      <c r="A92" s="62"/>
       <c r="B92" s="33" t="s">
         <v>142</v>
       </c>
@@ -5159,7 +5159,7 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="59"/>
+      <c r="A93" s="62"/>
       <c r="B93" s="33" t="s">
         <v>143</v>
       </c>
@@ -5194,7 +5194,7 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="60"/>
+      <c r="A94" s="63"/>
       <c r="B94" s="33" t="s">
         <v>144</v>
       </c>
@@ -5221,7 +5221,7 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="61">
+      <c r="A95" s="64">
         <v>14</v>
       </c>
       <c r="B95" s="31" t="s">
@@ -5266,7 +5266,7 @@
       <c r="U95" s="14"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="62"/>
+      <c r="A96" s="65"/>
       <c r="B96" s="31" t="s">
         <v>146</v>
       </c>
@@ -5307,7 +5307,7 @@
       <c r="U96" s="14"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="62"/>
+      <c r="A97" s="65"/>
       <c r="B97" s="31" t="s">
         <v>147</v>
       </c>
@@ -5362,7 +5362,7 @@
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="62"/>
+      <c r="A98" s="65"/>
       <c r="B98" s="31" t="s">
         <v>149</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="U98" s="14"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="62"/>
+      <c r="A99" s="65"/>
       <c r="B99" s="31" t="s">
         <v>150</v>
       </c>
@@ -5446,7 +5446,7 @@
       <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="62"/>
+      <c r="A100" s="65"/>
       <c r="B100" s="31" t="s">
         <v>151</v>
       </c>
@@ -5497,7 +5497,7 @@
       <c r="U100" s="14"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="63"/>
+      <c r="A101" s="66"/>
       <c r="B101" s="31" t="s">
         <v>152</v>
       </c>
@@ -5524,7 +5524,7 @@
       <c r="U101" s="14"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="58">
+      <c r="A102" s="61">
         <v>15</v>
       </c>
       <c r="B102" s="33" t="s">
@@ -5569,7 +5569,7 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="59"/>
+      <c r="A103" s="62"/>
       <c r="B103" s="33" t="s">
         <v>154</v>
       </c>
@@ -5612,7 +5612,7 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="59"/>
+      <c r="A104" s="62"/>
       <c r="B104" s="33" t="s">
         <v>155</v>
       </c>
@@ -5667,7 +5667,7 @@
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="59"/>
+      <c r="A105" s="62"/>
       <c r="B105" s="33" t="s">
         <v>156</v>
       </c>
@@ -5710,7 +5710,7 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="59"/>
+      <c r="A106" s="62"/>
       <c r="B106" s="33" t="s">
         <v>157</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="59"/>
+      <c r="A107" s="62"/>
       <c r="B107" s="33" t="s">
         <v>158</v>
       </c>
@@ -5788,7 +5788,7 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="60"/>
+      <c r="A108" s="63"/>
       <c r="B108" s="33" t="s">
         <v>159</v>
       </c>
@@ -5815,7 +5815,7 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="61">
+      <c r="A109" s="64">
         <v>16</v>
       </c>
       <c r="B109" s="31" t="s">
@@ -5860,7 +5860,7 @@
       <c r="U109" s="35"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="62"/>
+      <c r="A110" s="65"/>
       <c r="B110" s="31" t="s">
         <v>161</v>
       </c>
@@ -5903,7 +5903,7 @@
       <c r="U110" s="35"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="62"/>
+      <c r="A111" s="65"/>
       <c r="B111" s="31" t="s">
         <v>162</v>
       </c>
@@ -5958,7 +5958,7 @@
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="62"/>
+      <c r="A112" s="65"/>
       <c r="B112" s="31" t="s">
         <v>163</v>
       </c>
@@ -6001,7 +6001,7 @@
       <c r="U112" s="35"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="62"/>
+      <c r="A113" s="65"/>
       <c r="B113" s="31" t="s">
         <v>164</v>
       </c>
@@ -6044,7 +6044,7 @@
       <c r="U113" s="35"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="62"/>
+      <c r="A114" s="65"/>
       <c r="B114" s="31" t="s">
         <v>165</v>
       </c>
@@ -6071,7 +6071,7 @@
       <c r="U114" s="35"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="63"/>
+      <c r="A115" s="66"/>
       <c r="B115" s="31" t="s">
         <v>166</v>
       </c>
@@ -6098,7 +6098,7 @@
       <c r="U115" s="35"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="58">
+      <c r="A116" s="61">
         <v>17</v>
       </c>
       <c r="B116" s="33" t="s">
@@ -6141,7 +6141,7 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="59"/>
+      <c r="A117" s="62"/>
       <c r="B117" s="33" t="s">
         <v>168</v>
       </c>
@@ -6182,7 +6182,7 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="59"/>
+      <c r="A118" s="62"/>
       <c r="B118" s="33" t="s">
         <v>169</v>
       </c>
@@ -6235,7 +6235,7 @@
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="59"/>
+      <c r="A119" s="62"/>
       <c r="B119" s="33" t="s">
         <v>170</v>
       </c>
@@ -6276,7 +6276,7 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="59"/>
+      <c r="A120" s="62"/>
       <c r="B120" s="33" t="s">
         <v>171</v>
       </c>
@@ -6319,7 +6319,7 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="59"/>
+      <c r="A121" s="62"/>
       <c r="B121" s="33" t="s">
         <v>172</v>
       </c>
@@ -6346,7 +6346,7 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="60"/>
+      <c r="A122" s="63"/>
       <c r="B122" s="33" t="s">
         <v>173</v>
       </c>
@@ -6373,7 +6373,7 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="61">
+      <c r="A123" s="64">
         <v>18</v>
       </c>
       <c r="B123" s="31" t="s">
@@ -6382,191 +6382,191 @@
       <c r="C123" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="49" t="s">
+      <c r="D123" s="73" t="s">
         <v>175</v>
       </c>
-      <c r="E123" s="50"/>
-      <c r="F123" s="50"/>
-      <c r="G123" s="50"/>
-      <c r="H123" s="50"/>
-      <c r="I123" s="50"/>
-      <c r="J123" s="50"/>
-      <c r="K123" s="50"/>
-      <c r="L123" s="50"/>
-      <c r="M123" s="50"/>
-      <c r="N123" s="50"/>
-      <c r="O123" s="50"/>
-      <c r="P123" s="50"/>
-      <c r="Q123" s="50"/>
-      <c r="R123" s="50"/>
-      <c r="S123" s="50"/>
-      <c r="T123" s="50"/>
-      <c r="U123" s="51"/>
+      <c r="E123" s="74"/>
+      <c r="F123" s="74"/>
+      <c r="G123" s="74"/>
+      <c r="H123" s="74"/>
+      <c r="I123" s="74"/>
+      <c r="J123" s="74"/>
+      <c r="K123" s="74"/>
+      <c r="L123" s="74"/>
+      <c r="M123" s="74"/>
+      <c r="N123" s="74"/>
+      <c r="O123" s="74"/>
+      <c r="P123" s="74"/>
+      <c r="Q123" s="74"/>
+      <c r="R123" s="74"/>
+      <c r="S123" s="74"/>
+      <c r="T123" s="74"/>
+      <c r="U123" s="75"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="62"/>
+      <c r="A124" s="65"/>
       <c r="B124" s="31" t="s">
         <v>176</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="52"/>
-      <c r="E124" s="53"/>
-      <c r="F124" s="53"/>
-      <c r="G124" s="53"/>
-      <c r="H124" s="53"/>
-      <c r="I124" s="53"/>
-      <c r="J124" s="53"/>
-      <c r="K124" s="53"/>
-      <c r="L124" s="53"/>
-      <c r="M124" s="53"/>
-      <c r="N124" s="53"/>
-      <c r="O124" s="53"/>
-      <c r="P124" s="53"/>
-      <c r="Q124" s="53"/>
-      <c r="R124" s="53"/>
-      <c r="S124" s="53"/>
-      <c r="T124" s="53"/>
-      <c r="U124" s="54"/>
+      <c r="D124" s="76"/>
+      <c r="E124" s="77"/>
+      <c r="F124" s="77"/>
+      <c r="G124" s="77"/>
+      <c r="H124" s="77"/>
+      <c r="I124" s="77"/>
+      <c r="J124" s="77"/>
+      <c r="K124" s="77"/>
+      <c r="L124" s="77"/>
+      <c r="M124" s="77"/>
+      <c r="N124" s="77"/>
+      <c r="O124" s="77"/>
+      <c r="P124" s="77"/>
+      <c r="Q124" s="77"/>
+      <c r="R124" s="77"/>
+      <c r="S124" s="77"/>
+      <c r="T124" s="77"/>
+      <c r="U124" s="78"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="62"/>
+      <c r="A125" s="65"/>
       <c r="B125" s="31" t="s">
         <v>177</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D125" s="52"/>
-      <c r="E125" s="53"/>
-      <c r="F125" s="53"/>
-      <c r="G125" s="53"/>
-      <c r="H125" s="53"/>
-      <c r="I125" s="53"/>
-      <c r="J125" s="53"/>
-      <c r="K125" s="53"/>
-      <c r="L125" s="53"/>
-      <c r="M125" s="53"/>
-      <c r="N125" s="53"/>
-      <c r="O125" s="53"/>
-      <c r="P125" s="53"/>
-      <c r="Q125" s="53"/>
-      <c r="R125" s="53"/>
-      <c r="S125" s="53"/>
-      <c r="T125" s="53"/>
-      <c r="U125" s="54"/>
+      <c r="D125" s="76"/>
+      <c r="E125" s="77"/>
+      <c r="F125" s="77"/>
+      <c r="G125" s="77"/>
+      <c r="H125" s="77"/>
+      <c r="I125" s="77"/>
+      <c r="J125" s="77"/>
+      <c r="K125" s="77"/>
+      <c r="L125" s="77"/>
+      <c r="M125" s="77"/>
+      <c r="N125" s="77"/>
+      <c r="O125" s="77"/>
+      <c r="P125" s="77"/>
+      <c r="Q125" s="77"/>
+      <c r="R125" s="77"/>
+      <c r="S125" s="77"/>
+      <c r="T125" s="77"/>
+      <c r="U125" s="78"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="62"/>
+      <c r="A126" s="65"/>
       <c r="B126" s="31" t="s">
         <v>178</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D126" s="52"/>
-      <c r="E126" s="53"/>
-      <c r="F126" s="53"/>
-      <c r="G126" s="53"/>
-      <c r="H126" s="53"/>
-      <c r="I126" s="53"/>
-      <c r="J126" s="53"/>
-      <c r="K126" s="53"/>
-      <c r="L126" s="53"/>
-      <c r="M126" s="53"/>
-      <c r="N126" s="53"/>
-      <c r="O126" s="53"/>
-      <c r="P126" s="53"/>
-      <c r="Q126" s="53"/>
-      <c r="R126" s="53"/>
-      <c r="S126" s="53"/>
-      <c r="T126" s="53"/>
-      <c r="U126" s="54"/>
+      <c r="D126" s="76"/>
+      <c r="E126" s="77"/>
+      <c r="F126" s="77"/>
+      <c r="G126" s="77"/>
+      <c r="H126" s="77"/>
+      <c r="I126" s="77"/>
+      <c r="J126" s="77"/>
+      <c r="K126" s="77"/>
+      <c r="L126" s="77"/>
+      <c r="M126" s="77"/>
+      <c r="N126" s="77"/>
+      <c r="O126" s="77"/>
+      <c r="P126" s="77"/>
+      <c r="Q126" s="77"/>
+      <c r="R126" s="77"/>
+      <c r="S126" s="77"/>
+      <c r="T126" s="77"/>
+      <c r="U126" s="78"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="62"/>
+      <c r="A127" s="65"/>
       <c r="B127" s="30" t="s">
         <v>179</v>
       </c>
       <c r="C127" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D127" s="52"/>
-      <c r="E127" s="53"/>
-      <c r="F127" s="53"/>
-      <c r="G127" s="53"/>
-      <c r="H127" s="53"/>
-      <c r="I127" s="53"/>
-      <c r="J127" s="53"/>
-      <c r="K127" s="53"/>
-      <c r="L127" s="53"/>
-      <c r="M127" s="53"/>
-      <c r="N127" s="53"/>
-      <c r="O127" s="53"/>
-      <c r="P127" s="53"/>
-      <c r="Q127" s="53"/>
-      <c r="R127" s="53"/>
-      <c r="S127" s="53"/>
-      <c r="T127" s="53"/>
-      <c r="U127" s="54"/>
+      <c r="D127" s="76"/>
+      <c r="E127" s="77"/>
+      <c r="F127" s="77"/>
+      <c r="G127" s="77"/>
+      <c r="H127" s="77"/>
+      <c r="I127" s="77"/>
+      <c r="J127" s="77"/>
+      <c r="K127" s="77"/>
+      <c r="L127" s="77"/>
+      <c r="M127" s="77"/>
+      <c r="N127" s="77"/>
+      <c r="O127" s="77"/>
+      <c r="P127" s="77"/>
+      <c r="Q127" s="77"/>
+      <c r="R127" s="77"/>
+      <c r="S127" s="77"/>
+      <c r="T127" s="77"/>
+      <c r="U127" s="78"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="62"/>
+      <c r="A128" s="65"/>
       <c r="B128" s="31" t="s">
         <v>180</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D128" s="52"/>
-      <c r="E128" s="53"/>
-      <c r="F128" s="53"/>
-      <c r="G128" s="53"/>
-      <c r="H128" s="53"/>
-      <c r="I128" s="53"/>
-      <c r="J128" s="53"/>
-      <c r="K128" s="53"/>
-      <c r="L128" s="53"/>
-      <c r="M128" s="53"/>
-      <c r="N128" s="53"/>
-      <c r="O128" s="53"/>
-      <c r="P128" s="53"/>
-      <c r="Q128" s="53"/>
-      <c r="R128" s="53"/>
-      <c r="S128" s="53"/>
-      <c r="T128" s="53"/>
-      <c r="U128" s="54"/>
+      <c r="D128" s="76"/>
+      <c r="E128" s="77"/>
+      <c r="F128" s="77"/>
+      <c r="G128" s="77"/>
+      <c r="H128" s="77"/>
+      <c r="I128" s="77"/>
+      <c r="J128" s="77"/>
+      <c r="K128" s="77"/>
+      <c r="L128" s="77"/>
+      <c r="M128" s="77"/>
+      <c r="N128" s="77"/>
+      <c r="O128" s="77"/>
+      <c r="P128" s="77"/>
+      <c r="Q128" s="77"/>
+      <c r="R128" s="77"/>
+      <c r="S128" s="77"/>
+      <c r="T128" s="77"/>
+      <c r="U128" s="78"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="63"/>
+      <c r="A129" s="66"/>
       <c r="B129" s="31" t="s">
         <v>181</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D129" s="52"/>
-      <c r="E129" s="53"/>
-      <c r="F129" s="53"/>
-      <c r="G129" s="53"/>
-      <c r="H129" s="53"/>
-      <c r="I129" s="53"/>
-      <c r="J129" s="53"/>
-      <c r="K129" s="53"/>
-      <c r="L129" s="53"/>
-      <c r="M129" s="53"/>
-      <c r="N129" s="53"/>
-      <c r="O129" s="53"/>
-      <c r="P129" s="53"/>
-      <c r="Q129" s="53"/>
-      <c r="R129" s="53"/>
-      <c r="S129" s="53"/>
-      <c r="T129" s="53"/>
-      <c r="U129" s="54"/>
+      <c r="D129" s="76"/>
+      <c r="E129" s="77"/>
+      <c r="F129" s="77"/>
+      <c r="G129" s="77"/>
+      <c r="H129" s="77"/>
+      <c r="I129" s="77"/>
+      <c r="J129" s="77"/>
+      <c r="K129" s="77"/>
+      <c r="L129" s="77"/>
+      <c r="M129" s="77"/>
+      <c r="N129" s="77"/>
+      <c r="O129" s="77"/>
+      <c r="P129" s="77"/>
+      <c r="Q129" s="77"/>
+      <c r="R129" s="77"/>
+      <c r="S129" s="77"/>
+      <c r="T129" s="77"/>
+      <c r="U129" s="78"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="58">
+      <c r="A130" s="61">
         <v>19</v>
       </c>
       <c r="B130" s="33" t="s">
@@ -6575,186 +6575,186 @@
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="52"/>
-      <c r="E130" s="53"/>
-      <c r="F130" s="53"/>
-      <c r="G130" s="53"/>
-      <c r="H130" s="53"/>
-      <c r="I130" s="53"/>
-      <c r="J130" s="53"/>
-      <c r="K130" s="53"/>
-      <c r="L130" s="53"/>
-      <c r="M130" s="53"/>
-      <c r="N130" s="53"/>
-      <c r="O130" s="53"/>
-      <c r="P130" s="53"/>
-      <c r="Q130" s="53"/>
-      <c r="R130" s="53"/>
-      <c r="S130" s="53"/>
-      <c r="T130" s="53"/>
-      <c r="U130" s="54"/>
+      <c r="D130" s="76"/>
+      <c r="E130" s="77"/>
+      <c r="F130" s="77"/>
+      <c r="G130" s="77"/>
+      <c r="H130" s="77"/>
+      <c r="I130" s="77"/>
+      <c r="J130" s="77"/>
+      <c r="K130" s="77"/>
+      <c r="L130" s="77"/>
+      <c r="M130" s="77"/>
+      <c r="N130" s="77"/>
+      <c r="O130" s="77"/>
+      <c r="P130" s="77"/>
+      <c r="Q130" s="77"/>
+      <c r="R130" s="77"/>
+      <c r="S130" s="77"/>
+      <c r="T130" s="77"/>
+      <c r="U130" s="78"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="59"/>
+      <c r="A131" s="62"/>
       <c r="B131" s="33" t="s">
         <v>183</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="52"/>
-      <c r="E131" s="53"/>
-      <c r="F131" s="53"/>
-      <c r="G131" s="53"/>
-      <c r="H131" s="53"/>
-      <c r="I131" s="53"/>
-      <c r="J131" s="53"/>
-      <c r="K131" s="53"/>
-      <c r="L131" s="53"/>
-      <c r="M131" s="53"/>
-      <c r="N131" s="53"/>
-      <c r="O131" s="53"/>
-      <c r="P131" s="53"/>
-      <c r="Q131" s="53"/>
-      <c r="R131" s="53"/>
-      <c r="S131" s="53"/>
-      <c r="T131" s="53"/>
-      <c r="U131" s="54"/>
+      <c r="D131" s="76"/>
+      <c r="E131" s="77"/>
+      <c r="F131" s="77"/>
+      <c r="G131" s="77"/>
+      <c r="H131" s="77"/>
+      <c r="I131" s="77"/>
+      <c r="J131" s="77"/>
+      <c r="K131" s="77"/>
+      <c r="L131" s="77"/>
+      <c r="M131" s="77"/>
+      <c r="N131" s="77"/>
+      <c r="O131" s="77"/>
+      <c r="P131" s="77"/>
+      <c r="Q131" s="77"/>
+      <c r="R131" s="77"/>
+      <c r="S131" s="77"/>
+      <c r="T131" s="77"/>
+      <c r="U131" s="78"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="59"/>
+      <c r="A132" s="62"/>
       <c r="B132" s="33" t="s">
         <v>184</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D132" s="52"/>
-      <c r="E132" s="53"/>
-      <c r="F132" s="53"/>
-      <c r="G132" s="53"/>
-      <c r="H132" s="53"/>
-      <c r="I132" s="53"/>
-      <c r="J132" s="53"/>
-      <c r="K132" s="53"/>
-      <c r="L132" s="53"/>
-      <c r="M132" s="53"/>
-      <c r="N132" s="53"/>
-      <c r="O132" s="53"/>
-      <c r="P132" s="53"/>
-      <c r="Q132" s="53"/>
-      <c r="R132" s="53"/>
-      <c r="S132" s="53"/>
-      <c r="T132" s="53"/>
-      <c r="U132" s="54"/>
+      <c r="D132" s="76"/>
+      <c r="E132" s="77"/>
+      <c r="F132" s="77"/>
+      <c r="G132" s="77"/>
+      <c r="H132" s="77"/>
+      <c r="I132" s="77"/>
+      <c r="J132" s="77"/>
+      <c r="K132" s="77"/>
+      <c r="L132" s="77"/>
+      <c r="M132" s="77"/>
+      <c r="N132" s="77"/>
+      <c r="O132" s="77"/>
+      <c r="P132" s="77"/>
+      <c r="Q132" s="77"/>
+      <c r="R132" s="77"/>
+      <c r="S132" s="77"/>
+      <c r="T132" s="77"/>
+      <c r="U132" s="78"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="59"/>
+      <c r="A133" s="62"/>
       <c r="B133" s="33" t="s">
         <v>185</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="52"/>
-      <c r="E133" s="53"/>
-      <c r="F133" s="53"/>
-      <c r="G133" s="53"/>
-      <c r="H133" s="53"/>
-      <c r="I133" s="53"/>
-      <c r="J133" s="53"/>
-      <c r="K133" s="53"/>
-      <c r="L133" s="53"/>
-      <c r="M133" s="53"/>
-      <c r="N133" s="53"/>
-      <c r="O133" s="53"/>
-      <c r="P133" s="53"/>
-      <c r="Q133" s="53"/>
-      <c r="R133" s="53"/>
-      <c r="S133" s="53"/>
-      <c r="T133" s="53"/>
-      <c r="U133" s="54"/>
+      <c r="D133" s="76"/>
+      <c r="E133" s="77"/>
+      <c r="F133" s="77"/>
+      <c r="G133" s="77"/>
+      <c r="H133" s="77"/>
+      <c r="I133" s="77"/>
+      <c r="J133" s="77"/>
+      <c r="K133" s="77"/>
+      <c r="L133" s="77"/>
+      <c r="M133" s="77"/>
+      <c r="N133" s="77"/>
+      <c r="O133" s="77"/>
+      <c r="P133" s="77"/>
+      <c r="Q133" s="77"/>
+      <c r="R133" s="77"/>
+      <c r="S133" s="77"/>
+      <c r="T133" s="77"/>
+      <c r="U133" s="78"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="59"/>
+      <c r="A134" s="62"/>
       <c r="B134" s="33" t="s">
         <v>186</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D134" s="52"/>
-      <c r="E134" s="53"/>
-      <c r="F134" s="53"/>
-      <c r="G134" s="53"/>
-      <c r="H134" s="53"/>
-      <c r="I134" s="53"/>
-      <c r="J134" s="53"/>
-      <c r="K134" s="53"/>
-      <c r="L134" s="53"/>
-      <c r="M134" s="53"/>
-      <c r="N134" s="53"/>
-      <c r="O134" s="53"/>
-      <c r="P134" s="53"/>
-      <c r="Q134" s="53"/>
-      <c r="R134" s="53"/>
-      <c r="S134" s="53"/>
-      <c r="T134" s="53"/>
-      <c r="U134" s="54"/>
+      <c r="D134" s="76"/>
+      <c r="E134" s="77"/>
+      <c r="F134" s="77"/>
+      <c r="G134" s="77"/>
+      <c r="H134" s="77"/>
+      <c r="I134" s="77"/>
+      <c r="J134" s="77"/>
+      <c r="K134" s="77"/>
+      <c r="L134" s="77"/>
+      <c r="M134" s="77"/>
+      <c r="N134" s="77"/>
+      <c r="O134" s="77"/>
+      <c r="P134" s="77"/>
+      <c r="Q134" s="77"/>
+      <c r="R134" s="77"/>
+      <c r="S134" s="77"/>
+      <c r="T134" s="77"/>
+      <c r="U134" s="78"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="59"/>
+      <c r="A135" s="62"/>
       <c r="B135" s="33" t="s">
         <v>187</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D135" s="52"/>
-      <c r="E135" s="53"/>
-      <c r="F135" s="53"/>
-      <c r="G135" s="53"/>
-      <c r="H135" s="53"/>
-      <c r="I135" s="53"/>
-      <c r="J135" s="53"/>
-      <c r="K135" s="53"/>
-      <c r="L135" s="53"/>
-      <c r="M135" s="53"/>
-      <c r="N135" s="53"/>
-      <c r="O135" s="53"/>
-      <c r="P135" s="53"/>
-      <c r="Q135" s="53"/>
-      <c r="R135" s="53"/>
-      <c r="S135" s="53"/>
-      <c r="T135" s="53"/>
-      <c r="U135" s="54"/>
+      <c r="D135" s="76"/>
+      <c r="E135" s="77"/>
+      <c r="F135" s="77"/>
+      <c r="G135" s="77"/>
+      <c r="H135" s="77"/>
+      <c r="I135" s="77"/>
+      <c r="J135" s="77"/>
+      <c r="K135" s="77"/>
+      <c r="L135" s="77"/>
+      <c r="M135" s="77"/>
+      <c r="N135" s="77"/>
+      <c r="O135" s="77"/>
+      <c r="P135" s="77"/>
+      <c r="Q135" s="77"/>
+      <c r="R135" s="77"/>
+      <c r="S135" s="77"/>
+      <c r="T135" s="77"/>
+      <c r="U135" s="78"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="60"/>
+      <c r="A136" s="63"/>
       <c r="B136" s="33" t="s">
         <v>188</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D136" s="55"/>
-      <c r="E136" s="56"/>
-      <c r="F136" s="56"/>
-      <c r="G136" s="56"/>
-      <c r="H136" s="56"/>
-      <c r="I136" s="56"/>
-      <c r="J136" s="56"/>
-      <c r="K136" s="56"/>
-      <c r="L136" s="56"/>
-      <c r="M136" s="56"/>
-      <c r="N136" s="56"/>
-      <c r="O136" s="56"/>
-      <c r="P136" s="56"/>
-      <c r="Q136" s="56"/>
-      <c r="R136" s="56"/>
-      <c r="S136" s="56"/>
-      <c r="T136" s="56"/>
-      <c r="U136" s="57"/>
+      <c r="D136" s="79"/>
+      <c r="E136" s="80"/>
+      <c r="F136" s="80"/>
+      <c r="G136" s="80"/>
+      <c r="H136" s="80"/>
+      <c r="I136" s="80"/>
+      <c r="J136" s="80"/>
+      <c r="K136" s="80"/>
+      <c r="L136" s="80"/>
+      <c r="M136" s="80"/>
+      <c r="N136" s="80"/>
+      <c r="O136" s="80"/>
+      <c r="P136" s="80"/>
+      <c r="Q136" s="80"/>
+      <c r="R136" s="80"/>
+      <c r="S136" s="80"/>
+      <c r="T136" s="80"/>
+      <c r="U136" s="81"/>
     </row>
     <row r="137" spans="1:21"/>
     <row r="138" spans="1:21"/>
@@ -6772,6 +6772,26 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -6788,26 +6808,6 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
